--- a/StructureDefinition-mii-lm-prozedur.xlsx
+++ b/StructureDefinition-mii-lm-prozedur.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="151">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.0</t>
+    <t>2026.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-09</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,6 +90,9 @@
     <t>Purpose</t>
   </si>
   <si>
+    <t>Define the information model for procedures independently of a concrete FHIR resource representation.</t>
+  </si>
+  <si>
     <t>Copyright</t>
   </si>
   <si>
@@ -114,9 +120,6 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>Derivation</t>
   </si>
   <si>
@@ -232,9 +235,6 @@
   </si>
   <si>
     <t>Mapping: Prozedur LogicalModel FHIR Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: RIM Mapping</t>
   </si>
   <si>
     <t>Prozedur</t>
@@ -267,9 +267,6 @@
 </t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Prozedur.id</t>
   </si>
   <si>
@@ -366,9 +363,6 @@
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Prozedur.OPSProzedurKodiert.VollstaendigerProzedurencode</t>
@@ -678,79 +672,83 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>3</v>
@@ -758,26 +756,26 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -787,7 +785,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL20"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.5546875" customWidth="true" bestFit="true"/>
@@ -826,122 +824,118 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="116.98046875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>72</v>
-      </c>
-      <c r="AL1" t="s" s="1">
         <v>73</v>
       </c>
     </row>
@@ -979,7 +973,7 @@
         <v>79</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1047,16 +1041,13 @@
       <c r="AK2" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AL2" t="s" s="2">
-        <v>83</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1067,25 +1058,25 @@
         <v>76</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1136,13 +1127,13 @@
         <v>75</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>75</v>
@@ -1152,21 +1143,18 @@
       </c>
       <c r="AK3" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL3" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
@@ -1185,16 +1173,16 @@
         <v>75</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M4" t="s" s="2">
+      <c r="N4" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1232,19 +1220,19 @@
         <v>75</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>76</v>
@@ -1256,21 +1244,18 @@
         <v>75</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL4" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1281,7 +1266,7 @@
         <v>76</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>75</v>
@@ -1293,13 +1278,13 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1350,13 +1335,13 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>75</v>
@@ -1365,18 +1350,15 @@
         <v>82</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AL5" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1387,25 +1369,25 @@
         <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1456,13 +1438,13 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>75</v>
@@ -1472,21 +1454,18 @@
       </c>
       <c r="AK6" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL6" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1505,16 +1484,16 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1552,19 +1531,19 @@
         <v>75</v>
       </c>
       <c r="AB7" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC7" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC7" t="s" s="2">
+      <c r="AD7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE7" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE7" t="s" s="2">
+      <c r="AF7" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -1576,25 +1555,22 @@
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1607,25 +1583,25 @@
         <v>75</v>
       </c>
       <c r="I8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="J8" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O8" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="P8" t="s" s="2">
         <v>75</v>
@@ -1674,7 +1650,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -1686,21 +1662,18 @@
         <v>75</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1711,7 +1684,7 @@
         <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>75</v>
@@ -1723,13 +1696,13 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1780,13 +1753,13 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>75</v>
@@ -1795,18 +1768,15 @@
         <v>75</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1817,7 +1787,7 @@
         <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>75</v>
@@ -1829,13 +1799,13 @@
         <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1886,13 +1856,13 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>75</v>
@@ -1901,18 +1871,15 @@
         <v>75</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>75</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1923,7 +1890,7 @@
         <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>75</v>
@@ -1935,13 +1902,13 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1992,13 +1959,13 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>75</v>
@@ -2007,18 +1974,15 @@
         <v>82</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>75</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2029,25 +1993,25 @@
         <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K12" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K12" t="s" s="2">
+      <c r="L12" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2098,13 +2062,13 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>75</v>
@@ -2114,21 +2078,18 @@
       </c>
       <c r="AK12" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2147,16 +2108,16 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2194,19 +2155,19 @@
         <v>75</v>
       </c>
       <c r="AB13" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC13" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC13" t="s" s="2">
+      <c r="AD13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE13" t="s" s="2">
+      <c r="AF13" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2218,25 +2179,22 @@
         <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2249,25 +2207,25 @@
         <v>75</v>
       </c>
       <c r="I14" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="J14" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="K14" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O14" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>75</v>
@@ -2316,7 +2274,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2328,21 +2286,18 @@
         <v>75</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2353,7 +2308,7 @@
         <v>76</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>75</v>
@@ -2365,13 +2320,13 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2422,13 +2377,13 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>75</v>
@@ -2437,18 +2392,15 @@
         <v>75</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>75</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2471,13 +2423,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2528,7 +2480,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2543,18 +2495,15 @@
         <v>75</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2565,7 +2514,7 @@
         <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>75</v>
@@ -2577,13 +2526,13 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2634,13 +2583,13 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>75</v>
@@ -2649,18 +2598,15 @@
         <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2668,10 +2614,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>75</v>
@@ -2683,13 +2629,13 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2740,13 +2686,13 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>75</v>
@@ -2755,18 +2701,15 @@
         <v>75</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>75</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2777,7 +2720,7 @@
         <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>75</v>
@@ -2789,13 +2732,13 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2846,13 +2789,13 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>75</v>
@@ -2861,18 +2804,15 @@
         <v>75</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>75</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2883,25 +2823,25 @@
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K20" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K20" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="L20" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2952,13 +2892,13 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>75</v>
@@ -2967,10 +2907,7 @@
         <v>75</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>75</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-mii-lm-prozedur.xlsx
+++ b/StructureDefinition-mii-lm-prozedur.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="156">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -428,6 +428,22 @@
   </si>
   <si>
     <t>Procedure.bodySite</t>
+  </si>
+  <si>
+    <t>Prozedur.DetaillierteAnatomischeStruktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(BodyStructure)
+</t>
+  </si>
+  <si>
+    <t>Detaillierte anatomische Struktur</t>
+  </si>
+  <si>
+    <t>Detaillierte Angaben zu der patientenbezogenen anatomischen Struktur oder Lokalisation, auf die sich die Prozedur bezieht. Das Element kann verwendet werden, wenn die kodierte Angabe der Körperstelle allein nicht die für den Anwendungsfall erforderliche Genauigkeit bietet.</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension('http://hl7.org/fhir/StructureDefinition/bodySite').valueReference</t>
   </si>
   <si>
     <t>Prozedur.Durchfuehrungsabsicht</t>
@@ -785,7 +801,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.5546875" customWidth="true" bestFit="true"/>
@@ -798,7 +814,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="21.45703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2514,7 +2530,7 @@
         <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>75</v>
@@ -2526,13 +2542,13 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2589,7 +2605,7 @@
         <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>75</v>
@@ -2598,15 +2614,15 @@
         <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2614,7 +2630,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>84</v>
@@ -2629,7 +2645,7 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>140</v>
@@ -2686,10 +2702,10 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>84</v>
@@ -2717,7 +2733,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>84</v>
@@ -2732,13 +2748,13 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2792,7 +2808,7 @@
         <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>84</v>
@@ -2804,15 +2820,15 @@
         <v>75</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2835,13 +2851,13 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2892,7 +2908,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -2907,7 +2923,110 @@
         <v>75</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-mii-lm-prozedur.xlsx
+++ b/StructureDefinition-mii-lm-prozedur.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
